--- a/docs/04-数据总表.xlsx
+++ b/docs/04-数据总表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\unit-test-coverage\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFDF4773-BE6C-4ACD-A9AD-EC789CE7A46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D545B8E3-4286-4C90-9CB3-BF0D2E636183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -626,7 +626,7 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100</c:v>
+                  <c:v>92.31</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>100</c:v>
@@ -2471,7 +2471,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>10.846153846153847</c:v>
+                  <c:v>11.192307692307692</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>17.692307692307693</c:v>
@@ -5405,12 +5405,12 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>628650</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>128588</xdr:rowOff>
+      <xdr:rowOff>128587</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>1304926</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>166688</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5426,8 +5426,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5414963" y="4929188"/>
-          <a:ext cx="4033838" cy="1409700"/>
+          <a:off x="5414963" y="4929187"/>
+          <a:ext cx="4033838" cy="1581151"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5471,7 +5471,31 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>四组可编译率均为 </a:t>
+            <a:t>人工、自带、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>LLM-B </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>三组可编译率均为 </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
@@ -5495,7 +5519,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>，与四份 </a:t>
+            <a:t>，</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
@@ -5507,7 +5531,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Maven </a:t>
+            <a:t>LLM-A </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0">
@@ -5519,7 +5543,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>日志 </a:t>
+            <a:t>为 </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
@@ -5531,7 +5555,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>BUILD SUCCESS</a:t>
+            <a:t>92.31%</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0">
@@ -5543,7 +5567,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>、失败 </a:t>
+            <a:t>（</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
@@ -5555,7 +5579,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>0 </a:t>
+            <a:t>24/26</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0">
@@ -5567,7 +5591,153 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>一致。</a:t>
+            <a:t>），是四组中唯一未达 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>100% </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>的组。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>LLM-A </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>的缺口来自 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>BitRotate</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PermutationCipher </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>两个案例超时无产出，并非代码编译报错；若按“有产出才计”口径会得 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>100%</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>，但按“总案例行数”口径应为 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>92.31%</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>。</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -5581,7 +5751,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>该指标已饱和，不能区分组间质量；</a:t>
+            <a:t>可编译率整体接近饱和，组间差异主要由 </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
@@ -5617,7 +5787,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>BitRotate/PermutationCipher </a:t>
+            <a:t>2 </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0">
@@ -5629,21 +5799,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>是“无测试文件”而非编译失败，按“是”计。</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>正文应说明“可编译率四组同为 </a:t>
+            <a:t>个缺失案例造成，正文应注明口径，避免与其他三组的 </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0">
@@ -5655,7 +5811,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>100%</a:t>
+            <a:t>100% </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0">
@@ -5667,7 +5823,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>，区分度不足，质量差异看覆盖率与冗余率”。</a:t>
+            <a:t>直接比较时误读。</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -6041,15 +6197,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>335755</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>66681</xdr:rowOff>
+      <xdr:colOff>354805</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>42868</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1550193</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>66681</xdr:rowOff>
+      <xdr:colOff>1569243</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>42868</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6077,15 +6233,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>376237</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>157163</xdr:rowOff>
+      <xdr:colOff>385762</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>161926</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1528762</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:colOff>1538287</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>138113</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6100,7 +6256,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5162550" y="9244013"/>
+          <a:off x="5172075" y="9420226"/>
           <a:ext cx="4510087" cy="1176337"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6858,7 +7014,7 @@
         <v>7</v>
       </c>
       <c r="E8" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2">
         <v>92.9</v>
@@ -7101,7 +7257,7 @@
         <v>5</v>
       </c>
       <c r="E17" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" s="2">
         <v>100</v>
@@ -7128,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="E18" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="2">
         <v>95</v>
@@ -7155,7 +7311,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F19" s="2">
         <v>90.9</v>
@@ -9553,7 +9709,7 @@
       </c>
       <c r="C2" s="4">
         <f>IFERROR(AVERAGEIF(明细!$B$2:$B$105,$A2,明细!$E$2:$E$105),"")</f>
-        <v>10.846153846153847</v>
+        <v>11.192307692307692</v>
       </c>
       <c r="D2" s="4">
         <f>IFERROR(COUNTIFS(明细!$B$2:$B$105,$A2,明细!$C$2:$C$105,"是")/(COUNTIFS(明细!$B$2:$B$105,$A2,明细!$C$2:$C$105,"是")+COUNTIFS(明细!$B$2:$B$105,$A2,明细!$C$2:$C$105,"否")-COUNTIFS(明细!$B$2:$B$105,$A2,明细!$D$2:$D$105,"—"))*100,"")</f>
@@ -9626,8 +9782,7 @@
         <v>11.375</v>
       </c>
       <c r="D4" s="4">
-        <f>IFERROR(COUNTIFS(明细!$B$2:$B$105,$A4,明细!$C$2:$C$105,"是")/(COUNTIFS(明细!$B$2:$B$105,$A4,明细!$C$2:$C$105,"是")+COUNTIFS(明细!$B$2:$B$105,$A4,明细!$C$2:$C$105,"否")-COUNTIFS(明细!$B$2:$B$105,$A4,明细!$D$2:$D$105,"—"))*100,"")</f>
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="E4" s="4">
         <f>IFERROR(AVERAGEIF(明细!$B$2:$B$105,$A4,明细!$F$2:$F$105),"")</f>
